--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:25</t>
+    <t xml:space="preserve">2026-09-09 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -111,6 +111,9 @@
     <t xml:space="preserve">Olivar</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:21</t>
+    <t xml:space="preserve">2026-09-17 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6203</v>
+        <v>6204</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>18.52</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6103</v>
+        <v>6203</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18.44</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6102</v>
+        <v>6103</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.59</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6105</v>
+        <v>6102</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16.66</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6205</v>
+        <v>6105</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15.1</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6101</v>
+        <v>6205</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15.06</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6108</v>
+        <v>6101</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10.83</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6108</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>10.83</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:16</t>
+    <t xml:space="preserve">2026-09-23 12:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:45</t>
+    <t xml:space="preserve">2026-10-01 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1201,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:02</t>
+    <t xml:space="preserve">2026-10-02 11:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:17</t>
+    <t xml:space="preserve">2026-10-02 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:45</t>
+    <t xml:space="preserve">2026-10-04 09:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2018_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:17</t>
+    <t xml:space="preserve">2026-10-05 11:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
